--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_119_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_119_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1745</v>
+        <v>2.2081</v>
       </c>
       <c r="E2" t="n">
         <v>2.7405</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5324</v>
       </c>
       <c r="G2" t="n">
         <v>1.345</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4178</v>
+        <v>-0.3842</v>
       </c>
       <c r="T2" t="n">
         <v>-0.0272</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3905</v>
+        <v>-0.3569</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6324</v>
+        <v>2.0706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4108</v>
+        <v>0.8827</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2216</v>
+        <v>1.188</v>
       </c>
       <c r="G3" t="n">
         <v>4.1421</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1154</v>
+        <v>-0.6772</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2192</v>
+        <v>-0.2528</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3011</v>
+        <v>1.0898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1086</v>
+        <v>0.0653</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1925</v>
+        <v>1.0245</v>
       </c>
       <c r="G4" t="n">
         <v>0.0502</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4424</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4086</v>
+        <v>-0.4518</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0338</v>
+        <v>-0.2018</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7694</v>
+        <v>0.6603</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9981</v>
+        <v>-1.5696</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7676</v>
+        <v>2.2299</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0441</v>
@@ -844,13 +844,13 @@
         <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9366</v>
+        <v>-1.0458</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.7177</v>
+        <v>-1.2891</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7811</v>
+        <v>0.2434</v>
       </c>
       <c r="V5" t="n">
         <v>2.2862</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4398</v>
+        <v>0.2666</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2353</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6751</v>
+        <v>0.998</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6509</v>
+        <v>-1.9094</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8548</v>
+        <v>-0.9255</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5057</v>
+        <v>-0.9838</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2474</v>
+        <v>-1.0805</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7338</v>
+        <v>-1.4684</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9812</v>
+        <v>0.3879</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5965</v>
+        <v>-0.8289</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8789</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4755</v>
+        <v>-1.3717</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4125</v>
+        <v>-1.2158</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4604</v>
+        <v>-0.7231</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0479</v>
+        <v>-0.4927</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0733</v>
+        <v>0.0061</v>
       </c>
       <c r="E7" t="n">
         <v>0.5783</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.505</v>
+        <v>-0.5722</v>
       </c>
       <c r="G7" t="n">
         <v>0.036</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>0.022</v>
+        <v>-0.0452</v>
       </c>
       <c r="T7" t="n">
         <v>0.4208</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3989</v>
+        <v>-0.4661</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1947</v>
+        <v>-0.0939</v>
       </c>
       <c r="E8" t="n">
         <v>-0.6935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4988</v>
+        <v>0.5996</v>
       </c>
       <c r="G8" t="n">
         <v>0.5266999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3967</v>
+        <v>-0.2959</v>
       </c>
       <c r="T8" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7886</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4435</v>
+        <v>-0.2083</v>
       </c>
       <c r="E9" t="n">
         <v>-2.4164</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9729</v>
+        <v>2.2082</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4206</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2032</v>
+        <v>-0.968</v>
       </c>
       <c r="T9" t="n">
         <v>-0.6326000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5706</v>
+        <v>-0.3354</v>
       </c>
       <c r="V9" t="n">
         <v>0.7886</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5151</v>
+        <v>-0.4867</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2779</v>
+        <v>-2.061</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7627</v>
+        <v>1.5743</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9094</v>
+        <v>0.6509</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9255</v>
+        <v>-0.8548</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9838</v>
+        <v>1.5057</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0805</v>
+        <v>1.2474</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4684</v>
+        <v>-1.7338</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3879</v>
+        <v>2.9812</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8289</v>
+        <v>-0.5965</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.8789</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3717</v>
+        <v>-1.4755</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9975</v>
+        <v>-0.514</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2696</v>
+        <v>-0.3653</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7279</v>
+        <v>-0.1487</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9293</v>
+        <v>-1.1077</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3285</v>
+        <v>-1.6077</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3992</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
         <v>1.1321</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1489</v>
+        <v>-0.3273</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>-0.2396</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1885</v>
+        <v>-0.0876</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5414</v>
+        <v>-3.2651</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2713</v>
+        <v>-5.1966</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7299</v>
+        <v>1.9316</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8285</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.695</v>
+        <v>-0.4187</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>-0.0272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.593</v>
+        <v>-0.3914</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7665000000000002</v>
+        <v>1.139800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.3828</v>
+        <v>-10.0094</v>
       </c>
       <c r="F13" t="n">
-        <v>11.1493</v>
+        <v>11.1495</v>
       </c>
       <c r="G13" t="n">
-        <v>1.680400000000001</v>
+        <v>1.6804</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6123</v>
+        <v>5.612299999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-3.931699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5918</v>
+        <v>3.591799999999999</v>
       </c>
       <c r="K13" t="n">
         <v>1.7026</v>
@@ -1456,7 +1456,7 @@
         <v>3.9094</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.821099999999999</v>
+        <v>-5.8211</v>
       </c>
       <c r="P13" t="n">
         <v>8.118299999999998</v>
@@ -1468,10 +1468,10 @@
         <v>22.0354</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.919000000000001</v>
+        <v>-6.545800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1252</v>
+        <v>-3.7516</v>
       </c>
       <c r="U13" t="n">
         <v>-2.7938</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2264</v>
+        <v>3.525</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7841</v>
+        <v>1.5457</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4423</v>
+        <v>1.9793</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9895</v>
+        <v>0.2354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9506</v>
+        <v>0.078</v>
       </c>
       <c r="I14" t="n">
-        <v>5.0389</v>
+        <v>0.1574</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8723</v>
+        <v>0.4535</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4053</v>
+        <v>0.3431</v>
       </c>
       <c r="L14" t="n">
-        <v>5.467</v>
+        <v>0.1104</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8828</v>
+        <v>-0.2181</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4547</v>
+        <v>-0.2651</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4281</v>
+        <v>0.047</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.7112</v>
+        <v>1.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.0307</v>
+        <v>-0.4639</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4842</v>
+        <v>0.8257</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9426</v>
+        <v>0.4839</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5417</v>
+        <v>0.3418</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4197</v>
+        <v>3.2999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1354</v>
+        <v>1.9585</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2843</v>
+        <v>1.3415</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2354</v>
+        <v>5.9895</v>
       </c>
       <c r="H15" t="n">
-        <v>0.078</v>
+        <v>0.9506</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1574</v>
+        <v>5.0389</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4535</v>
+        <v>6.8723</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3431</v>
+        <v>1.4053</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1104</v>
+        <v>5.467</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2181</v>
+        <v>-0.8828</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2651</v>
+        <v>-0.4547</v>
       </c>
       <c r="O15" t="n">
-        <v>0.047</v>
+        <v>-0.4281</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4639</v>
+        <v>-6.0307</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7204</v>
+        <v>1.5578</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0736</v>
+        <v>1.1169</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3532</v>
+        <v>0.4408</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5698</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0553</v>
+        <v>-0.7704</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5145</v>
+        <v>1.7054</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2493</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3552</v>
+        <v>0.7205</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9831</v>
+        <v>0.1575</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3721</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. PLAVSIC</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1956</v>
+        <v>0.6919</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0994</v>
+        <v>-0.781</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0963</v>
+        <v>1.4729</v>
       </c>
       <c r="G17" t="n">
-        <v>0.099</v>
+        <v>-0.2353</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0048</v>
+        <v>-0.2822</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1038</v>
+        <v>0.0469</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0168</v>
+        <v>0.3471</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0168</v>
+        <v>-0.2283</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.5754</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0822</v>
+        <v>-0.5825</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0216</v>
+        <v>-0.0539</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1038</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.3705</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0141</v>
+        <v>0.3389</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.091</v>
+        <v>0.1309</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3198</v>
+        <v>-0.2018</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4108</v>
+        <v>0.3328</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2003</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2913</v>
+        <v>0.3312</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4327</v>
+        <v>0.3547</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>U. PLAVSIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.052</v>
+        <v>0.1284</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2528</v>
+        <v>0.0994</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3048</v>
+        <v>0.029</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2353</v>
+        <v>0.099</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2822</v>
+        <v>-0.0048</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0469</v>
+        <v>0.1038</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3471</v>
+        <v>0.0168</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2283</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5754</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5825</v>
+        <v>0.0822</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0539</v>
+        <v>-0.0216</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5286</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2693</v>
+        <v>0.0294</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4402</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1709</v>
+        <v>-0.0532</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5784</v>
+        <v>-0.6615</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1116</v>
+        <v>-2.7577</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5331</v>
+        <v>2.0962</v>
       </c>
       <c r="G20" t="n">
         <v>0.0024</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8314</v>
+        <v>1.7484</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0633</v>
+        <v>0.4171</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7682</v>
+        <v>1.3313</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7728</v>
+        <v>-0.762</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2062</v>
+        <v>-2.2626</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4334</v>
+        <v>1.5007</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1082</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2934</v>
+        <v>0.7174</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5737</v>
+        <v>0.3699</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2803</v>
+        <v>0.3475</v>
       </c>
       <c r="V21" t="n">
         <v>1.8608</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4755</v>
+        <v>-1.9308</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3275</v>
+        <v>-2.9737</v>
       </c>
       <c r="F22" t="n">
-        <v>0.852</v>
+        <v>1.0429</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7117</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1428</v>
+        <v>0.402</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2592</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1164</v>
+        <v>0.3073</v>
       </c>
       <c r="V22" t="n">
         <v>2.5387</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7248</v>
+        <v>-2.3934</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3482</v>
+        <v>-2.5395</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3767</v>
+        <v>0.1461</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7191</v>
+        <v>-1.2209</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6722</v>
+        <v>-1.9135</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0469</v>
+        <v>0.6926</v>
       </c>
       <c r="J23" t="n">
-        <v>1.001</v>
+        <v>-0.967</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1078</v>
+        <v>-1.5559</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8932</v>
+        <v>0.5889</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.282</v>
+        <v>-0.2539</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5644</v>
+        <v>-0.3577</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8464</v>
+        <v>0.1038</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>1.234</v>
+        <v>-0.0127</v>
       </c>
       <c r="T23" t="n">
-        <v>0.362</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
-        <v>0.872</v>
+        <v>0.168</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7694</v>
+        <v>-2.9436</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6574</v>
+        <v>-2.4661</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.112</v>
+        <v>-0.4775</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2209</v>
+        <v>0.7191</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9135</v>
+        <v>0.6722</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6926</v>
+        <v>0.0469</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.967</v>
+        <v>1.001</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5559</v>
+        <v>0.1078</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5889</v>
+        <v>0.8932</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2539</v>
+        <v>-0.282</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3577</v>
+        <v>0.5644</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1038</v>
+        <v>-0.8464</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3888</v>
+        <v>1.0152</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>0.244</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0901</v>
+        <v>0.7712</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7664</v>
+        <v>0.01979999999999782</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.1493</v>
+        <v>-11.1492</v>
       </c>
       <c r="F25" t="n">
-        <v>10.3828</v>
+        <v>11.1693</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6803</v>
+        <v>-1.680300000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-5.6122</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>6.918799999999999</v>
+        <v>7.7054</v>
       </c>
       <c r="T25" t="n">
-        <v>2.793900000000001</v>
+        <v>2.7939</v>
       </c>
       <c r="U25" t="n">
-        <v>4.125100000000001</v>
+        <v>4.9113</v>
       </c>
       <c r="V25" t="n">
         <v>2.1133</v>
